--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:15:17+00:00</t>
+    <t>2026-06-15T08:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:40:43+00:00</t>
+    <t>2026-06-15T08:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:59:58+00:00</t>
+    <t>2026-06-18T07:59:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T07:59:27+00:00</t>
+    <t>2026-06-18T08:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:58+00:00</t>
+    <t>2026-06-18T08:53:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:27+00:00</t>
+    <t>2026-06-18T08:56:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:56:30+00:00</t>
+    <t>2026-06-18T10:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:39:29+00:00</t>
+    <t>2026-06-18T11:30:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:30:08+00:00</t>
+    <t>2026-06-23T16:45:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:45:59+00:00</t>
+    <t>2026-06-24T07:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:38:46+00:00</t>
+    <t>2026-06-25T15:12:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:12:52+00:00</t>
+    <t>2026-07-10T09:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T09:26:12+00:00</t>
+    <t>2026-07-20T12:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:02:06+00:00</t>
+    <t>2026-07-20T15:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:05:40+00:00</t>
+    <t>2026-07-27T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/ValueSet-onko-therapy-goal-type.xlsx
+++ b/ci-build/ValueSet-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
